--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12395,10 +12395,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862758</v>
+        <v>119862761</v>
       </c>
       <c r="B112" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12411,54 +12411,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585399</v>
+        <v>585371</v>
       </c>
       <c r="R112" t="n">
-        <v>7040847</v>
+        <v>7040884</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12491,11 +12471,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12522,7 +12497,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862810</v>
+        <v>119862758</v>
       </c>
       <c r="B113" t="n">
         <v>57310</v>
@@ -12555,12 +12530,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12570,10 +12557,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585359</v>
+        <v>585399</v>
       </c>
       <c r="R113" t="n">
-        <v>7041095</v>
+        <v>7040847</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12606,6 +12593,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12632,10 +12624,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862761</v>
+        <v>119862810</v>
       </c>
       <c r="B114" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12648,34 +12640,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585371</v>
+        <v>585359</v>
       </c>
       <c r="R114" t="n">
-        <v>7040884</v>
+        <v>7041095</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12395,10 +12395,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862761</v>
+        <v>119862758</v>
       </c>
       <c r="B112" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12411,34 +12411,54 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585371</v>
+        <v>585399</v>
       </c>
       <c r="R112" t="n">
-        <v>7040884</v>
+        <v>7040847</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12471,6 +12491,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12497,7 +12522,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862758</v>
+        <v>119862810</v>
       </c>
       <c r="B113" t="n">
         <v>57310</v>
@@ -12530,24 +12555,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12557,10 +12570,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585399</v>
+        <v>585359</v>
       </c>
       <c r="R113" t="n">
-        <v>7040847</v>
+        <v>7041095</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12593,11 +12606,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12624,10 +12632,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862810</v>
+        <v>119862761</v>
       </c>
       <c r="B114" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12640,42 +12648,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585359</v>
+        <v>585371</v>
       </c>
       <c r="R114" t="n">
-        <v>7041095</v>
+        <v>7040884</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10840,10 +10840,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119862754</v>
+        <v>119862766</v>
       </c>
       <c r="B97" t="n">
-        <v>90576</v>
+        <v>90562</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10856,21 +10856,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585410</v>
+        <v>585385</v>
       </c>
       <c r="R97" t="n">
-        <v>7040863</v>
+        <v>7040831</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10942,10 +10942,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862759</v>
+        <v>119862763</v>
       </c>
       <c r="B98" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10958,54 +10958,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585371</v>
+        <v>585388</v>
       </c>
       <c r="R98" t="n">
-        <v>7040883</v>
+        <v>7040836</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11038,11 +11018,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11069,10 +11044,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862767</v>
+        <v>119862755</v>
       </c>
       <c r="B99" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11081,25 +11056,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11109,10 +11084,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585354</v>
+        <v>585395</v>
       </c>
       <c r="R99" t="n">
-        <v>7040772</v>
+        <v>7040859</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11171,10 +11146,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862768</v>
+        <v>119862757</v>
       </c>
       <c r="B100" t="n">
-        <v>90576</v>
+        <v>90846</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11187,21 +11162,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11211,10 +11186,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585352</v>
+        <v>585395</v>
       </c>
       <c r="R100" t="n">
-        <v>7040764</v>
+        <v>7040848</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11273,10 +11248,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862762</v>
+        <v>119862768</v>
       </c>
       <c r="B101" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11289,21 +11264,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11313,10 +11288,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585380</v>
+        <v>585352</v>
       </c>
       <c r="R101" t="n">
-        <v>7040800</v>
+        <v>7040764</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11375,10 +11350,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862769</v>
+        <v>119862756</v>
       </c>
       <c r="B102" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11391,21 +11366,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11415,10 +11390,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585361</v>
+        <v>585395</v>
       </c>
       <c r="R102" t="n">
-        <v>7040752</v>
+        <v>7040848</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11477,10 +11452,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862766</v>
+        <v>119862769</v>
       </c>
       <c r="B103" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11493,21 +11468,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11517,10 +11492,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585385</v>
+        <v>585361</v>
       </c>
       <c r="R103" t="n">
-        <v>7040831</v>
+        <v>7040752</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11579,10 +11554,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119862755</v>
+        <v>119862753</v>
       </c>
       <c r="B104" t="n">
-        <v>90580</v>
+        <v>95455</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11595,21 +11570,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11619,10 +11594,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585395</v>
+        <v>585405</v>
       </c>
       <c r="R104" t="n">
-        <v>7040859</v>
+        <v>7040862</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11681,10 +11656,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119862764</v>
+        <v>119862758</v>
       </c>
       <c r="B105" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11697,34 +11672,54 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585387</v>
+        <v>585399</v>
       </c>
       <c r="R105" t="n">
-        <v>7040839</v>
+        <v>7040847</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11757,6 +11752,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11783,10 +11783,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119862757</v>
+        <v>119862759</v>
       </c>
       <c r="B106" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11799,34 +11799,54 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585395</v>
+        <v>585371</v>
       </c>
       <c r="R106" t="n">
-        <v>7040848</v>
+        <v>7040883</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11859,6 +11879,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11885,10 +11910,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119862752</v>
+        <v>119862760</v>
       </c>
       <c r="B107" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11897,25 +11922,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11925,10 +11950,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585403</v>
+        <v>585372</v>
       </c>
       <c r="R107" t="n">
-        <v>7040860</v>
+        <v>7040881</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11987,10 +12012,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119862753</v>
+        <v>119862762</v>
       </c>
       <c r="B108" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12003,21 +12028,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12027,10 +12052,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585405</v>
+        <v>585380</v>
       </c>
       <c r="R108" t="n">
-        <v>7040862</v>
+        <v>7040800</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12089,10 +12114,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862756</v>
+        <v>119862767</v>
       </c>
       <c r="B109" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12101,25 +12126,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12129,10 +12154,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585395</v>
+        <v>585354</v>
       </c>
       <c r="R109" t="n">
-        <v>7040848</v>
+        <v>7040772</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12191,10 +12216,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862760</v>
+        <v>119862752</v>
       </c>
       <c r="B110" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12203,25 +12228,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12231,10 +12256,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585372</v>
+        <v>585403</v>
       </c>
       <c r="R110" t="n">
-        <v>7040881</v>
+        <v>7040860</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12293,10 +12318,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862765</v>
+        <v>119862810</v>
       </c>
       <c r="B111" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12309,34 +12334,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585382</v>
+        <v>585359</v>
       </c>
       <c r="R111" t="n">
-        <v>7040827</v>
+        <v>7041095</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12395,10 +12428,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862758</v>
+        <v>119862764</v>
       </c>
       <c r="B112" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12411,54 +12444,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585399</v>
+        <v>585387</v>
       </c>
       <c r="R112" t="n">
-        <v>7040847</v>
+        <v>7040839</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12491,11 +12504,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12522,10 +12530,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862810</v>
+        <v>119862761</v>
       </c>
       <c r="B113" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12538,42 +12546,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585359</v>
+        <v>585371</v>
       </c>
       <c r="R113" t="n">
-        <v>7041095</v>
+        <v>7040884</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862761</v>
+        <v>119862754</v>
       </c>
       <c r="B114" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12648,21 +12648,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12672,10 +12672,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585371</v>
+        <v>585410</v>
       </c>
       <c r="R114" t="n">
-        <v>7040884</v>
+        <v>7040863</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12734,10 +12734,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862763</v>
+        <v>119862765</v>
       </c>
       <c r="B115" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12750,21 +12750,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585388</v>
+        <v>585382</v>
       </c>
       <c r="R115" t="n">
-        <v>7040836</v>
+        <v>7040827</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10840,10 +10840,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119862766</v>
+        <v>119862757</v>
       </c>
       <c r="B97" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10856,21 +10856,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585385</v>
+        <v>585395</v>
       </c>
       <c r="R97" t="n">
-        <v>7040831</v>
+        <v>7040848</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10942,10 +10942,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862763</v>
+        <v>119862754</v>
       </c>
       <c r="B98" t="n">
-        <v>90562</v>
+        <v>90576</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10958,21 +10958,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10982,10 +10982,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585388</v>
+        <v>585410</v>
       </c>
       <c r="R98" t="n">
-        <v>7040836</v>
+        <v>7040863</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11044,10 +11044,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862755</v>
+        <v>119862762</v>
       </c>
       <c r="B99" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11060,21 +11060,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585395</v>
+        <v>585380</v>
       </c>
       <c r="R99" t="n">
-        <v>7040859</v>
+        <v>7040800</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11146,10 +11146,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862757</v>
+        <v>119862810</v>
       </c>
       <c r="B100" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11162,34 +11162,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585395</v>
+        <v>585359</v>
       </c>
       <c r="R100" t="n">
-        <v>7040848</v>
+        <v>7041095</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11248,10 +11256,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862768</v>
+        <v>119862763</v>
       </c>
       <c r="B101" t="n">
-        <v>90576</v>
+        <v>90562</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11264,21 +11272,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11288,10 +11296,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585352</v>
+        <v>585388</v>
       </c>
       <c r="R101" t="n">
-        <v>7040764</v>
+        <v>7040836</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11350,10 +11358,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862756</v>
+        <v>119862760</v>
       </c>
       <c r="B102" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11362,25 +11370,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11390,10 +11398,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585395</v>
+        <v>585372</v>
       </c>
       <c r="R102" t="n">
-        <v>7040848</v>
+        <v>7040881</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11452,7 +11460,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862769</v>
+        <v>119862764</v>
       </c>
       <c r="B103" t="n">
         <v>90846</v>
@@ -11492,10 +11500,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585361</v>
+        <v>585387</v>
       </c>
       <c r="R103" t="n">
-        <v>7040752</v>
+        <v>7040839</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11554,10 +11562,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119862753</v>
+        <v>119862758</v>
       </c>
       <c r="B104" t="n">
-        <v>95455</v>
+        <v>57310</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11570,34 +11578,54 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585405</v>
+        <v>585399</v>
       </c>
       <c r="R104" t="n">
-        <v>7040862</v>
+        <v>7040847</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11630,6 +11658,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11656,10 +11689,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119862758</v>
+        <v>119862769</v>
       </c>
       <c r="B105" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11672,54 +11705,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585399</v>
+        <v>585361</v>
       </c>
       <c r="R105" t="n">
-        <v>7040847</v>
+        <v>7040752</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11752,11 +11765,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11783,10 +11791,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119862759</v>
+        <v>119862753</v>
       </c>
       <c r="B106" t="n">
-        <v>57310</v>
+        <v>95455</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11799,54 +11807,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585371</v>
+        <v>585405</v>
       </c>
       <c r="R106" t="n">
-        <v>7040883</v>
+        <v>7040862</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11879,11 +11867,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11910,10 +11893,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119862760</v>
+        <v>119862768</v>
       </c>
       <c r="B107" t="n">
-        <v>97907</v>
+        <v>90576</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11922,25 +11905,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11950,10 +11933,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585372</v>
+        <v>585352</v>
       </c>
       <c r="R107" t="n">
-        <v>7040881</v>
+        <v>7040764</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12012,10 +11995,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119862762</v>
+        <v>119862752</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12028,21 +12011,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12052,10 +12035,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585380</v>
+        <v>585403</v>
       </c>
       <c r="R108" t="n">
-        <v>7040800</v>
+        <v>7040860</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12114,10 +12097,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862767</v>
+        <v>119862766</v>
       </c>
       <c r="B109" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12126,25 +12109,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12154,10 +12137,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585354</v>
+        <v>585385</v>
       </c>
       <c r="R109" t="n">
-        <v>7040772</v>
+        <v>7040831</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12216,10 +12199,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862752</v>
+        <v>119862756</v>
       </c>
       <c r="B110" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12232,21 +12215,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12256,10 +12239,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585403</v>
+        <v>585395</v>
       </c>
       <c r="R110" t="n">
-        <v>7040860</v>
+        <v>7040848</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12318,10 +12301,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862810</v>
+        <v>119862767</v>
       </c>
       <c r="B111" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12330,46 +12313,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585359</v>
+        <v>585354</v>
       </c>
       <c r="R111" t="n">
-        <v>7041095</v>
+        <v>7040772</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12428,7 +12403,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862764</v>
+        <v>119862765</v>
       </c>
       <c r="B112" t="n">
         <v>90846</v>
@@ -12468,10 +12443,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585387</v>
+        <v>585382</v>
       </c>
       <c r="R112" t="n">
-        <v>7040839</v>
+        <v>7040827</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12530,10 +12505,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862761</v>
+        <v>119862759</v>
       </c>
       <c r="B113" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12546,24 +12521,44 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
@@ -12573,7 +12568,7 @@
         <v>585371</v>
       </c>
       <c r="R113" t="n">
-        <v>7040884</v>
+        <v>7040883</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12606,6 +12601,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12632,10 +12632,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862754</v>
+        <v>119862761</v>
       </c>
       <c r="B114" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12648,21 +12648,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12672,10 +12672,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585410</v>
+        <v>585371</v>
       </c>
       <c r="R114" t="n">
-        <v>7040863</v>
+        <v>7040884</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12734,10 +12734,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862765</v>
+        <v>119862755</v>
       </c>
       <c r="B115" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12750,21 +12750,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585382</v>
+        <v>585395</v>
       </c>
       <c r="R115" t="n">
-        <v>7040827</v>
+        <v>7040859</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10942,10 +10942,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862754</v>
+        <v>119862810</v>
       </c>
       <c r="B98" t="n">
-        <v>90576</v>
+        <v>57310</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10958,34 +10958,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585410</v>
+        <v>585359</v>
       </c>
       <c r="R98" t="n">
-        <v>7040863</v>
+        <v>7041095</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11044,10 +11052,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862762</v>
+        <v>119862754</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11060,21 +11068,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11084,10 +11092,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585380</v>
+        <v>585410</v>
       </c>
       <c r="R99" t="n">
-        <v>7040800</v>
+        <v>7040863</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11146,10 +11154,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862810</v>
+        <v>119862762</v>
       </c>
       <c r="B100" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11162,42 +11170,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585359</v>
+        <v>585380</v>
       </c>
       <c r="R100" t="n">
-        <v>7041095</v>
+        <v>7040800</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11995,10 +11995,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119862752</v>
+        <v>119862766</v>
       </c>
       <c r="B108" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12011,21 +12011,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12035,10 +12035,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585403</v>
+        <v>585385</v>
       </c>
       <c r="R108" t="n">
-        <v>7040860</v>
+        <v>7040831</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12097,10 +12097,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862766</v>
+        <v>119862752</v>
       </c>
       <c r="B109" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12113,21 +12113,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12137,10 +12137,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585385</v>
+        <v>585403</v>
       </c>
       <c r="R109" t="n">
-        <v>7040831</v>
+        <v>7040860</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10840,10 +10840,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119862757</v>
+        <v>119862756</v>
       </c>
       <c r="B97" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10856,21 +10856,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862754</v>
+        <v>119862763</v>
       </c>
       <c r="B99" t="n">
-        <v>90576</v>
+        <v>90562</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11068,21 +11068,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11092,10 +11092,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585410</v>
+        <v>585388</v>
       </c>
       <c r="R99" t="n">
-        <v>7040863</v>
+        <v>7040836</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11154,10 +11154,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862762</v>
+        <v>119862766</v>
       </c>
       <c r="B100" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11170,21 +11170,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11194,10 +11194,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585380</v>
+        <v>585385</v>
       </c>
       <c r="R100" t="n">
-        <v>7040800</v>
+        <v>7040831</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11256,10 +11256,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862763</v>
+        <v>119862765</v>
       </c>
       <c r="B101" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11272,21 +11272,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585388</v>
+        <v>585382</v>
       </c>
       <c r="R101" t="n">
-        <v>7040836</v>
+        <v>7040827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11358,10 +11358,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862760</v>
+        <v>119862762</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11370,25 +11370,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11398,10 +11398,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585372</v>
+        <v>585380</v>
       </c>
       <c r="R102" t="n">
-        <v>7040881</v>
+        <v>7040800</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11460,7 +11460,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862764</v>
+        <v>119862757</v>
       </c>
       <c r="B103" t="n">
         <v>90846</v>
@@ -11500,10 +11500,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585387</v>
+        <v>585395</v>
       </c>
       <c r="R103" t="n">
-        <v>7040839</v>
+        <v>7040848</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11562,10 +11562,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119862758</v>
+        <v>119862752</v>
       </c>
       <c r="B104" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11578,54 +11578,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585399</v>
+        <v>585403</v>
       </c>
       <c r="R104" t="n">
-        <v>7040847</v>
+        <v>7040860</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11658,11 +11638,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11689,10 +11664,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119862769</v>
+        <v>119862759</v>
       </c>
       <c r="B105" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11705,34 +11680,54 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585361</v>
+        <v>585371</v>
       </c>
       <c r="R105" t="n">
-        <v>7040752</v>
+        <v>7040883</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11765,6 +11760,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11791,10 +11791,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119862753</v>
+        <v>119862758</v>
       </c>
       <c r="B106" t="n">
-        <v>95455</v>
+        <v>57310</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11807,34 +11807,54 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585405</v>
+        <v>585399</v>
       </c>
       <c r="R106" t="n">
-        <v>7040862</v>
+        <v>7040847</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11867,6 +11887,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11893,10 +11918,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119862768</v>
+        <v>119862764</v>
       </c>
       <c r="B107" t="n">
-        <v>90576</v>
+        <v>90846</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11909,21 +11934,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11933,10 +11958,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585352</v>
+        <v>585387</v>
       </c>
       <c r="R107" t="n">
-        <v>7040764</v>
+        <v>7040839</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11995,10 +12020,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119862766</v>
+        <v>119862760</v>
       </c>
       <c r="B108" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12007,25 +12032,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12035,10 +12060,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585385</v>
+        <v>585372</v>
       </c>
       <c r="R108" t="n">
-        <v>7040831</v>
+        <v>7040881</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12097,10 +12122,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862752</v>
+        <v>119862767</v>
       </c>
       <c r="B109" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12109,25 +12134,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12137,10 +12162,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585403</v>
+        <v>585354</v>
       </c>
       <c r="R109" t="n">
-        <v>7040860</v>
+        <v>7040772</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12199,10 +12224,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862756</v>
+        <v>119862769</v>
       </c>
       <c r="B110" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12215,21 +12240,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12239,10 +12264,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585395</v>
+        <v>585361</v>
       </c>
       <c r="R110" t="n">
-        <v>7040848</v>
+        <v>7040752</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12301,10 +12326,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862767</v>
+        <v>119862754</v>
       </c>
       <c r="B111" t="n">
-        <v>90527</v>
+        <v>90576</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12313,25 +12338,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12341,10 +12366,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585354</v>
+        <v>585410</v>
       </c>
       <c r="R111" t="n">
-        <v>7040772</v>
+        <v>7040863</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12403,10 +12428,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862765</v>
+        <v>119862755</v>
       </c>
       <c r="B112" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12419,21 +12444,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12443,10 +12468,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585382</v>
+        <v>585395</v>
       </c>
       <c r="R112" t="n">
-        <v>7040827</v>
+        <v>7040859</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12505,10 +12530,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862759</v>
+        <v>119862768</v>
       </c>
       <c r="B113" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12521,54 +12546,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585371</v>
+        <v>585352</v>
       </c>
       <c r="R113" t="n">
-        <v>7040883</v>
+        <v>7040764</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12601,11 +12606,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12632,10 +12632,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862761</v>
+        <v>119862753</v>
       </c>
       <c r="B114" t="n">
-        <v>90580</v>
+        <v>95455</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12648,21 +12648,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12672,10 +12672,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585371</v>
+        <v>585405</v>
       </c>
       <c r="R114" t="n">
-        <v>7040884</v>
+        <v>7040862</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12734,7 +12734,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862755</v>
+        <v>119862761</v>
       </c>
       <c r="B115" t="n">
         <v>90580</v>
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585395</v>
+        <v>585371</v>
       </c>
       <c r="R115" t="n">
-        <v>7040859</v>
+        <v>7040884</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12122,10 +12122,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862767</v>
+        <v>119862754</v>
       </c>
       <c r="B109" t="n">
-        <v>90527</v>
+        <v>90576</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12134,25 +12134,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12162,10 +12162,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585354</v>
+        <v>585410</v>
       </c>
       <c r="R109" t="n">
-        <v>7040772</v>
+        <v>7040863</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12224,10 +12224,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862769</v>
+        <v>119862767</v>
       </c>
       <c r="B110" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12236,25 +12236,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585361</v>
+        <v>585354</v>
       </c>
       <c r="R110" t="n">
-        <v>7040752</v>
+        <v>7040772</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862754</v>
+        <v>119862769</v>
       </c>
       <c r="B111" t="n">
-        <v>90576</v>
+        <v>90846</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12342,21 +12342,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12366,10 +12366,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585410</v>
+        <v>585361</v>
       </c>
       <c r="R111" t="n">
-        <v>7040863</v>
+        <v>7040752</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12122,10 +12122,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862754</v>
+        <v>119862767</v>
       </c>
       <c r="B109" t="n">
-        <v>90576</v>
+        <v>90527</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12134,25 +12134,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12162,10 +12162,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585410</v>
+        <v>585354</v>
       </c>
       <c r="R109" t="n">
-        <v>7040863</v>
+        <v>7040772</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12224,10 +12224,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862767</v>
+        <v>119862769</v>
       </c>
       <c r="B110" t="n">
-        <v>90527</v>
+        <v>90846</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12236,25 +12236,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12264,10 +12264,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585354</v>
+        <v>585361</v>
       </c>
       <c r="R110" t="n">
-        <v>7040772</v>
+        <v>7040752</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12326,10 +12326,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862769</v>
+        <v>119862754</v>
       </c>
       <c r="B111" t="n">
-        <v>90846</v>
+        <v>90576</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12342,21 +12342,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12366,10 +12366,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585361</v>
+        <v>585410</v>
       </c>
       <c r="R111" t="n">
-        <v>7040752</v>
+        <v>7040863</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10840,10 +10840,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119862756</v>
+        <v>119862761</v>
       </c>
       <c r="B97" t="n">
-        <v>90562</v>
+        <v>90598</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10856,21 +10856,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585395</v>
+        <v>585371</v>
       </c>
       <c r="R97" t="n">
-        <v>7040848</v>
+        <v>7040884</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10942,10 +10942,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862810</v>
+        <v>119862758</v>
       </c>
       <c r="B98" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10975,12 +10975,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -10990,10 +11002,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585359</v>
+        <v>585399</v>
       </c>
       <c r="R98" t="n">
-        <v>7041095</v>
+        <v>7040847</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11026,6 +11038,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11052,10 +11069,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862763</v>
+        <v>119862767</v>
       </c>
       <c r="B99" t="n">
-        <v>90562</v>
+        <v>90545</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11064,25 +11081,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11092,10 +11109,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585388</v>
+        <v>585354</v>
       </c>
       <c r="R99" t="n">
-        <v>7040836</v>
+        <v>7040772</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11154,10 +11171,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862766</v>
+        <v>119862753</v>
       </c>
       <c r="B100" t="n">
-        <v>90562</v>
+        <v>95478</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11170,21 +11187,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11194,10 +11211,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585385</v>
+        <v>585405</v>
       </c>
       <c r="R100" t="n">
-        <v>7040831</v>
+        <v>7040862</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11256,10 +11273,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862765</v>
+        <v>119862763</v>
       </c>
       <c r="B101" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11272,21 +11289,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11296,10 +11313,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585382</v>
+        <v>585388</v>
       </c>
       <c r="R101" t="n">
-        <v>7040827</v>
+        <v>7040836</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11358,10 +11375,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862762</v>
+        <v>119862769</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>90864</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11374,21 +11391,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11398,10 +11415,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585380</v>
+        <v>585361</v>
       </c>
       <c r="R102" t="n">
-        <v>7040800</v>
+        <v>7040752</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11460,10 +11477,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862757</v>
+        <v>119862762</v>
       </c>
       <c r="B103" t="n">
-        <v>90846</v>
+        <v>78542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11476,21 +11493,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11500,10 +11517,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585395</v>
+        <v>585380</v>
       </c>
       <c r="R103" t="n">
-        <v>7040848</v>
+        <v>7040800</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11562,10 +11579,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119862752</v>
+        <v>119862760</v>
       </c>
       <c r="B104" t="n">
-        <v>90846</v>
+        <v>97930</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11574,25 +11591,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11602,10 +11619,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585403</v>
+        <v>585372</v>
       </c>
       <c r="R104" t="n">
-        <v>7040860</v>
+        <v>7040881</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11664,10 +11681,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119862759</v>
+        <v>119862756</v>
       </c>
       <c r="B105" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11680,54 +11697,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585371</v>
+        <v>585395</v>
       </c>
       <c r="R105" t="n">
-        <v>7040883</v>
+        <v>7040848</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11760,11 +11757,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11791,10 +11783,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119862758</v>
+        <v>119862764</v>
       </c>
       <c r="B106" t="n">
-        <v>57310</v>
+        <v>90864</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11807,54 +11799,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585399</v>
+        <v>585387</v>
       </c>
       <c r="R106" t="n">
-        <v>7040847</v>
+        <v>7040839</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11887,11 +11859,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11918,10 +11885,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119862764</v>
+        <v>119862752</v>
       </c>
       <c r="B107" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11958,10 +11925,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585387</v>
+        <v>585403</v>
       </c>
       <c r="R107" t="n">
-        <v>7040839</v>
+        <v>7040860</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12020,10 +11987,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119862760</v>
+        <v>119862755</v>
       </c>
       <c r="B108" t="n">
-        <v>97907</v>
+        <v>90598</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12032,25 +11999,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12060,10 +12027,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585372</v>
+        <v>585395</v>
       </c>
       <c r="R108" t="n">
-        <v>7040881</v>
+        <v>7040859</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12125,7 +12092,7 @@
         <v>119862754</v>
       </c>
       <c r="B109" t="n">
-        <v>90576</v>
+        <v>90594</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12224,10 +12191,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862767</v>
+        <v>119862810</v>
       </c>
       <c r="B110" t="n">
-        <v>90527</v>
+        <v>57320</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12236,38 +12203,46 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585354</v>
+        <v>585359</v>
       </c>
       <c r="R110" t="n">
-        <v>7040772</v>
+        <v>7041095</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12326,10 +12301,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862769</v>
+        <v>119862768</v>
       </c>
       <c r="B111" t="n">
-        <v>90846</v>
+        <v>90594</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12342,21 +12317,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12366,10 +12341,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585361</v>
+        <v>585352</v>
       </c>
       <c r="R111" t="n">
-        <v>7040752</v>
+        <v>7040764</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12428,10 +12403,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862755</v>
+        <v>119862765</v>
       </c>
       <c r="B112" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12444,21 +12419,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12468,10 +12443,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585395</v>
+        <v>585382</v>
       </c>
       <c r="R112" t="n">
-        <v>7040859</v>
+        <v>7040827</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12530,10 +12505,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862768</v>
+        <v>119862766</v>
       </c>
       <c r="B113" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12546,21 +12521,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12570,10 +12545,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585352</v>
+        <v>585385</v>
       </c>
       <c r="R113" t="n">
-        <v>7040764</v>
+        <v>7040831</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12632,10 +12607,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862753</v>
+        <v>119862757</v>
       </c>
       <c r="B114" t="n">
-        <v>95455</v>
+        <v>90864</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12648,21 +12623,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12672,10 +12647,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585405</v>
+        <v>585395</v>
       </c>
       <c r="R114" t="n">
-        <v>7040862</v>
+        <v>7040848</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12734,10 +12709,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862761</v>
+        <v>119862759</v>
       </c>
       <c r="B115" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12750,24 +12725,44 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
@@ -12777,7 +12772,7 @@
         <v>585371</v>
       </c>
       <c r="R115" t="n">
-        <v>7040884</v>
+        <v>7040883</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12810,6 +12805,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10942,10 +10942,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862758</v>
+        <v>119862767</v>
       </c>
       <c r="B98" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10954,58 +10954,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585399</v>
+        <v>585354</v>
       </c>
       <c r="R98" t="n">
-        <v>7040847</v>
+        <v>7040772</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11038,11 +11018,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11069,10 +11044,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862767</v>
+        <v>119862758</v>
       </c>
       <c r="B99" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11081,38 +11056,58 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585354</v>
+        <v>585399</v>
       </c>
       <c r="R99" t="n">
-        <v>7040772</v>
+        <v>7040847</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11145,6 +11140,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11171,10 +11171,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862753</v>
+        <v>119862763</v>
       </c>
       <c r="B100" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11187,21 +11187,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585405</v>
+        <v>585388</v>
       </c>
       <c r="R100" t="n">
-        <v>7040862</v>
+        <v>7040836</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862763</v>
+        <v>119862753</v>
       </c>
       <c r="B101" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11289,21 +11289,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585388</v>
+        <v>585405</v>
       </c>
       <c r="R101" t="n">
-        <v>7040836</v>
+        <v>7040862</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862769</v>
+        <v>119862762</v>
       </c>
       <c r="B102" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11391,21 +11391,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585361</v>
+        <v>585380</v>
       </c>
       <c r="R102" t="n">
-        <v>7040752</v>
+        <v>7040800</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11477,10 +11477,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862762</v>
+        <v>119862769</v>
       </c>
       <c r="B103" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11493,21 +11493,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11517,10 +11517,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585380</v>
+        <v>585361</v>
       </c>
       <c r="R103" t="n">
-        <v>7040800</v>
+        <v>7040752</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10840,10 +10840,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119862761</v>
+        <v>119862756</v>
       </c>
       <c r="B97" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10856,21 +10856,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585371</v>
+        <v>585395</v>
       </c>
       <c r="R97" t="n">
-        <v>7040884</v>
+        <v>7040848</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10942,10 +10942,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862767</v>
+        <v>119862769</v>
       </c>
       <c r="B98" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10954,25 +10954,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10982,10 +10982,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585354</v>
+        <v>585361</v>
       </c>
       <c r="R98" t="n">
-        <v>7040772</v>
+        <v>7040752</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11044,7 +11044,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862758</v>
+        <v>119862759</v>
       </c>
       <c r="B99" t="n">
         <v>57320</v>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -11104,10 +11104,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585399</v>
+        <v>585371</v>
       </c>
       <c r="R99" t="n">
-        <v>7040847</v>
+        <v>7040883</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
+          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11171,10 +11171,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862763</v>
+        <v>119862753</v>
       </c>
       <c r="B100" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11187,21 +11187,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585388</v>
+        <v>585405</v>
       </c>
       <c r="R100" t="n">
-        <v>7040836</v>
+        <v>7040862</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862753</v>
+        <v>119862761</v>
       </c>
       <c r="B101" t="n">
-        <v>95478</v>
+        <v>90598</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11289,21 +11289,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585405</v>
+        <v>585371</v>
       </c>
       <c r="R101" t="n">
-        <v>7040862</v>
+        <v>7040884</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862762</v>
+        <v>119862764</v>
       </c>
       <c r="B102" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11391,21 +11391,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585380</v>
+        <v>585387</v>
       </c>
       <c r="R102" t="n">
-        <v>7040800</v>
+        <v>7040839</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11477,10 +11477,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862769</v>
+        <v>119862758</v>
       </c>
       <c r="B103" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11493,34 +11493,54 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585361</v>
+        <v>585399</v>
       </c>
       <c r="R103" t="n">
-        <v>7040752</v>
+        <v>7040847</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11553,6 +11573,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11579,10 +11604,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119862760</v>
+        <v>119862768</v>
       </c>
       <c r="B104" t="n">
-        <v>97930</v>
+        <v>90594</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11591,25 +11616,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11619,10 +11644,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585372</v>
+        <v>585352</v>
       </c>
       <c r="R104" t="n">
-        <v>7040881</v>
+        <v>7040764</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11681,10 +11706,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119862756</v>
+        <v>119862765</v>
       </c>
       <c r="B105" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11697,21 +11722,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11721,10 +11746,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585395</v>
+        <v>585382</v>
       </c>
       <c r="R105" t="n">
-        <v>7040848</v>
+        <v>7040827</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11783,10 +11808,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119862764</v>
+        <v>119862766</v>
       </c>
       <c r="B106" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11799,21 +11824,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11823,10 +11848,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585387</v>
+        <v>585385</v>
       </c>
       <c r="R106" t="n">
-        <v>7040839</v>
+        <v>7040831</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11987,10 +12012,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119862755</v>
+        <v>119862763</v>
       </c>
       <c r="B108" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12003,21 +12028,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12027,10 +12052,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585395</v>
+        <v>585388</v>
       </c>
       <c r="R108" t="n">
-        <v>7040859</v>
+        <v>7040836</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12089,10 +12114,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862754</v>
+        <v>119862757</v>
       </c>
       <c r="B109" t="n">
-        <v>90594</v>
+        <v>90864</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12105,21 +12130,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12129,10 +12154,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585410</v>
+        <v>585395</v>
       </c>
       <c r="R109" t="n">
-        <v>7040863</v>
+        <v>7040848</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12191,10 +12216,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862810</v>
+        <v>119862762</v>
       </c>
       <c r="B110" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12207,42 +12232,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585359</v>
+        <v>585380</v>
       </c>
       <c r="R110" t="n">
-        <v>7041095</v>
+        <v>7040800</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12301,10 +12318,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862768</v>
+        <v>119862810</v>
       </c>
       <c r="B111" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12317,34 +12334,42 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585352</v>
+        <v>585359</v>
       </c>
       <c r="R111" t="n">
-        <v>7040764</v>
+        <v>7041095</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12403,10 +12428,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862765</v>
+        <v>119862755</v>
       </c>
       <c r="B112" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12419,21 +12444,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12443,10 +12468,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585382</v>
+        <v>585395</v>
       </c>
       <c r="R112" t="n">
-        <v>7040827</v>
+        <v>7040859</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12505,10 +12530,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862766</v>
+        <v>119862754</v>
       </c>
       <c r="B113" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12521,21 +12546,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12545,10 +12570,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585385</v>
+        <v>585410</v>
       </c>
       <c r="R113" t="n">
-        <v>7040831</v>
+        <v>7040863</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12607,10 +12632,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862757</v>
+        <v>119862767</v>
       </c>
       <c r="B114" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12619,25 +12644,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12647,10 +12672,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585395</v>
+        <v>585354</v>
       </c>
       <c r="R114" t="n">
-        <v>7040848</v>
+        <v>7040772</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12709,10 +12734,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862759</v>
+        <v>119862760</v>
       </c>
       <c r="B115" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12721,58 +12746,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585371</v>
+        <v>585372</v>
       </c>
       <c r="R115" t="n">
-        <v>7040883</v>
+        <v>7040881</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12805,11 +12810,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10840,10 +10840,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119862756</v>
+        <v>119862810</v>
       </c>
       <c r="B97" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10856,34 +10856,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585395</v>
+        <v>585359</v>
       </c>
       <c r="R97" t="n">
-        <v>7040848</v>
+        <v>7041095</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10942,10 +10950,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862769</v>
+        <v>119862760</v>
       </c>
       <c r="B98" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10954,25 +10962,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10982,10 +10990,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585361</v>
+        <v>585372</v>
       </c>
       <c r="R98" t="n">
-        <v>7040752</v>
+        <v>7040881</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11044,10 +11052,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862759</v>
+        <v>119862756</v>
       </c>
       <c r="B99" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11060,54 +11068,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585371</v>
+        <v>585395</v>
       </c>
       <c r="R99" t="n">
-        <v>7040883</v>
+        <v>7040848</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11140,11 +11128,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11273,10 +11256,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862761</v>
+        <v>119862762</v>
       </c>
       <c r="B101" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11289,21 +11272,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11313,10 +11296,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585371</v>
+        <v>585380</v>
       </c>
       <c r="R101" t="n">
-        <v>7040884</v>
+        <v>7040800</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11375,7 +11358,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862764</v>
+        <v>119862752</v>
       </c>
       <c r="B102" t="n">
         <v>90864</v>
@@ -11415,10 +11398,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585387</v>
+        <v>585403</v>
       </c>
       <c r="R102" t="n">
-        <v>7040839</v>
+        <v>7040860</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11477,10 +11460,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862758</v>
+        <v>119862754</v>
       </c>
       <c r="B103" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11493,54 +11476,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585399</v>
+        <v>585410</v>
       </c>
       <c r="R103" t="n">
-        <v>7040847</v>
+        <v>7040863</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11573,11 +11536,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11604,10 +11562,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119862768</v>
+        <v>119862767</v>
       </c>
       <c r="B104" t="n">
-        <v>90594</v>
+        <v>90545</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11616,25 +11574,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11644,10 +11602,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585352</v>
+        <v>585354</v>
       </c>
       <c r="R104" t="n">
-        <v>7040764</v>
+        <v>7040772</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11706,7 +11664,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119862765</v>
+        <v>119862769</v>
       </c>
       <c r="B105" t="n">
         <v>90864</v>
@@ -11746,10 +11704,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585382</v>
+        <v>585361</v>
       </c>
       <c r="R105" t="n">
-        <v>7040827</v>
+        <v>7040752</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11808,10 +11766,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119862766</v>
+        <v>119862758</v>
       </c>
       <c r="B106" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11824,34 +11782,54 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585385</v>
+        <v>585399</v>
       </c>
       <c r="R106" t="n">
-        <v>7040831</v>
+        <v>7040847</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11884,6 +11862,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11910,10 +11893,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119862752</v>
+        <v>119862761</v>
       </c>
       <c r="B107" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11926,21 +11909,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11950,10 +11933,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585403</v>
+        <v>585371</v>
       </c>
       <c r="R107" t="n">
-        <v>7040860</v>
+        <v>7040884</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12114,10 +12097,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862757</v>
+        <v>119862768</v>
       </c>
       <c r="B109" t="n">
-        <v>90864</v>
+        <v>90594</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12130,21 +12113,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12154,10 +12137,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585395</v>
+        <v>585352</v>
       </c>
       <c r="R109" t="n">
-        <v>7040848</v>
+        <v>7040764</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12216,10 +12199,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862762</v>
+        <v>119862757</v>
       </c>
       <c r="B110" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12232,21 +12215,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12256,10 +12239,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585380</v>
+        <v>585395</v>
       </c>
       <c r="R110" t="n">
-        <v>7040800</v>
+        <v>7040848</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12318,10 +12301,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862810</v>
+        <v>119862766</v>
       </c>
       <c r="B111" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12334,42 +12317,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585359</v>
+        <v>585385</v>
       </c>
       <c r="R111" t="n">
-        <v>7041095</v>
+        <v>7040831</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12428,10 +12403,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862755</v>
+        <v>119862759</v>
       </c>
       <c r="B112" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12444,34 +12419,54 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585395</v>
+        <v>585371</v>
       </c>
       <c r="R112" t="n">
-        <v>7040859</v>
+        <v>7040883</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12504,6 +12499,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12530,10 +12530,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862754</v>
+        <v>119862755</v>
       </c>
       <c r="B113" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12546,21 +12546,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12570,10 +12570,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585410</v>
+        <v>585395</v>
       </c>
       <c r="R113" t="n">
-        <v>7040863</v>
+        <v>7040859</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862767</v>
+        <v>119862764</v>
       </c>
       <c r="B114" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12644,25 +12644,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12672,10 +12672,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585354</v>
+        <v>585387</v>
       </c>
       <c r="R114" t="n">
-        <v>7040772</v>
+        <v>7040839</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12734,10 +12734,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862760</v>
+        <v>119862765</v>
       </c>
       <c r="B115" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12746,25 +12746,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585372</v>
+        <v>585382</v>
       </c>
       <c r="R115" t="n">
-        <v>7040881</v>
+        <v>7040827</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12530,10 +12530,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862755</v>
+        <v>119862764</v>
       </c>
       <c r="B113" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12546,21 +12546,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12570,10 +12570,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585395</v>
+        <v>585387</v>
       </c>
       <c r="R113" t="n">
-        <v>7040859</v>
+        <v>7040839</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12632,7 +12632,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862764</v>
+        <v>119862765</v>
       </c>
       <c r="B114" t="n">
         <v>90864</v>
@@ -12672,10 +12672,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585387</v>
+        <v>585382</v>
       </c>
       <c r="R114" t="n">
-        <v>7040839</v>
+        <v>7040827</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12734,10 +12734,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862765</v>
+        <v>119862755</v>
       </c>
       <c r="B115" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12750,21 +12750,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585382</v>
+        <v>585395</v>
       </c>
       <c r="R115" t="n">
-        <v>7040827</v>
+        <v>7040859</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10840,7 +10840,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119862810</v>
+        <v>119862759</v>
       </c>
       <c r="B97" t="n">
         <v>57320</v>
@@ -10873,12 +10873,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10888,10 +10900,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585359</v>
+        <v>585371</v>
       </c>
       <c r="R97" t="n">
-        <v>7041095</v>
+        <v>7040883</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10924,6 +10936,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10950,10 +10967,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862760</v>
+        <v>119862762</v>
       </c>
       <c r="B98" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10962,25 +10979,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10990,10 +11007,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585372</v>
+        <v>585380</v>
       </c>
       <c r="R98" t="n">
-        <v>7040881</v>
+        <v>7040800</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11052,10 +11069,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862756</v>
+        <v>119862754</v>
       </c>
       <c r="B99" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11068,21 +11085,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11092,10 +11109,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585395</v>
+        <v>585410</v>
       </c>
       <c r="R99" t="n">
-        <v>7040848</v>
+        <v>7040863</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11154,10 +11171,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862753</v>
+        <v>119862766</v>
       </c>
       <c r="B100" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11170,21 +11187,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11194,10 +11211,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585405</v>
+        <v>585385</v>
       </c>
       <c r="R100" t="n">
-        <v>7040862</v>
+        <v>7040831</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11256,10 +11273,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862762</v>
+        <v>119862765</v>
       </c>
       <c r="B101" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11272,21 +11289,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11296,10 +11313,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585380</v>
+        <v>585382</v>
       </c>
       <c r="R101" t="n">
-        <v>7040800</v>
+        <v>7040827</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11358,10 +11375,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862752</v>
+        <v>119862756</v>
       </c>
       <c r="B102" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11374,21 +11391,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11398,10 +11415,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585403</v>
+        <v>585395</v>
       </c>
       <c r="R102" t="n">
-        <v>7040860</v>
+        <v>7040848</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11460,10 +11477,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862754</v>
+        <v>119862761</v>
       </c>
       <c r="B103" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11476,21 +11493,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11500,10 +11517,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585410</v>
+        <v>585371</v>
       </c>
       <c r="R103" t="n">
-        <v>7040863</v>
+        <v>7040884</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11562,10 +11579,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119862767</v>
+        <v>119862755</v>
       </c>
       <c r="B104" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11574,25 +11591,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11602,10 +11619,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>585354</v>
+        <v>585395</v>
       </c>
       <c r="R104" t="n">
-        <v>7040772</v>
+        <v>7040859</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11664,7 +11681,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119862769</v>
+        <v>119862757</v>
       </c>
       <c r="B105" t="n">
         <v>90864</v>
@@ -11704,10 +11721,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585361</v>
+        <v>585395</v>
       </c>
       <c r="R105" t="n">
-        <v>7040752</v>
+        <v>7040848</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11766,10 +11783,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119862758</v>
+        <v>119862752</v>
       </c>
       <c r="B106" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11782,54 +11799,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585399</v>
+        <v>585403</v>
       </c>
       <c r="R106" t="n">
-        <v>7040847</v>
+        <v>7040860</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11862,11 +11859,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11893,10 +11885,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119862761</v>
+        <v>119862758</v>
       </c>
       <c r="B107" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11909,34 +11901,54 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585371</v>
+        <v>585399</v>
       </c>
       <c r="R107" t="n">
-        <v>7040884</v>
+        <v>7040847</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11969,6 +11981,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11995,10 +12012,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119862763</v>
+        <v>119862769</v>
       </c>
       <c r="B108" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12011,21 +12028,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12035,10 +12052,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585388</v>
+        <v>585361</v>
       </c>
       <c r="R108" t="n">
-        <v>7040836</v>
+        <v>7040752</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12097,10 +12114,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862768</v>
+        <v>119862763</v>
       </c>
       <c r="B109" t="n">
-        <v>90594</v>
+        <v>90580</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12113,21 +12130,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12137,10 +12154,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585352</v>
+        <v>585388</v>
       </c>
       <c r="R109" t="n">
-        <v>7040764</v>
+        <v>7040836</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12199,10 +12216,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862757</v>
+        <v>119862753</v>
       </c>
       <c r="B110" t="n">
-        <v>90864</v>
+        <v>95478</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12215,21 +12232,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12239,10 +12256,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585395</v>
+        <v>585405</v>
       </c>
       <c r="R110" t="n">
-        <v>7040848</v>
+        <v>7040862</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12301,10 +12318,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862766</v>
+        <v>119862768</v>
       </c>
       <c r="B111" t="n">
-        <v>90580</v>
+        <v>90594</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12317,21 +12334,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12341,10 +12358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585385</v>
+        <v>585352</v>
       </c>
       <c r="R111" t="n">
-        <v>7040831</v>
+        <v>7040764</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12403,7 +12420,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862759</v>
+        <v>119862810</v>
       </c>
       <c r="B112" t="n">
         <v>57320</v>
@@ -12436,24 +12453,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -12463,10 +12468,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585371</v>
+        <v>585359</v>
       </c>
       <c r="R112" t="n">
-        <v>7040883</v>
+        <v>7041095</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12499,11 +12504,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12530,10 +12530,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862764</v>
+        <v>119862767</v>
       </c>
       <c r="B113" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12542,25 +12542,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12570,10 +12570,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585387</v>
+        <v>585354</v>
       </c>
       <c r="R113" t="n">
-        <v>7040839</v>
+        <v>7040772</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862765</v>
+        <v>119862760</v>
       </c>
       <c r="B114" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12644,25 +12644,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12672,10 +12672,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585382</v>
+        <v>585372</v>
       </c>
       <c r="R114" t="n">
-        <v>7040827</v>
+        <v>7040881</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12734,10 +12734,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862755</v>
+        <v>119862764</v>
       </c>
       <c r="B115" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12750,21 +12750,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12774,10 +12774,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585395</v>
+        <v>585387</v>
       </c>
       <c r="R115" t="n">
-        <v>7040859</v>
+        <v>7040839</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -10840,10 +10840,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119862759</v>
+        <v>119862756</v>
       </c>
       <c r="B97" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10856,54 +10856,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>585371</v>
+        <v>585395</v>
       </c>
       <c r="R97" t="n">
-        <v>7040883</v>
+        <v>7040848</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10936,11 +10916,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10967,10 +10942,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119862762</v>
+        <v>119862765</v>
       </c>
       <c r="B98" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10983,21 +10958,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11007,10 +10982,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>585380</v>
+        <v>585382</v>
       </c>
       <c r="R98" t="n">
-        <v>7040800</v>
+        <v>7040827</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11069,10 +11044,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119862754</v>
+        <v>119862755</v>
       </c>
       <c r="B99" t="n">
-        <v>90594</v>
+        <v>90598</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11085,21 +11060,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11109,10 +11084,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>585410</v>
+        <v>585395</v>
       </c>
       <c r="R99" t="n">
-        <v>7040863</v>
+        <v>7040859</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11171,10 +11146,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119862766</v>
+        <v>119862761</v>
       </c>
       <c r="B100" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11187,21 +11162,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11211,10 +11186,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>585385</v>
+        <v>585371</v>
       </c>
       <c r="R100" t="n">
-        <v>7040831</v>
+        <v>7040884</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11273,10 +11248,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119862765</v>
+        <v>119862759</v>
       </c>
       <c r="B101" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11289,34 +11264,54 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>585382</v>
+        <v>585371</v>
       </c>
       <c r="R101" t="n">
-        <v>7040827</v>
+        <v>7040883</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11349,6 +11344,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11375,10 +11375,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119862756</v>
+        <v>119862760</v>
       </c>
       <c r="B102" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11387,25 +11387,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>585395</v>
+        <v>585372</v>
       </c>
       <c r="R102" t="n">
-        <v>7040848</v>
+        <v>7040881</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11477,10 +11477,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119862761</v>
+        <v>119862763</v>
       </c>
       <c r="B103" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11493,21 +11493,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11517,10 +11517,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>585371</v>
+        <v>585388</v>
       </c>
       <c r="R103" t="n">
-        <v>7040884</v>
+        <v>7040836</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11579,10 +11579,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119862755</v>
+        <v>119862757</v>
       </c>
       <c r="B104" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11595,21 +11595,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11622,7 +11622,7 @@
         <v>585395</v>
       </c>
       <c r="R104" t="n">
-        <v>7040859</v>
+        <v>7040848</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11681,10 +11681,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119862757</v>
+        <v>119862766</v>
       </c>
       <c r="B105" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11697,21 +11697,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>585395</v>
+        <v>585385</v>
       </c>
       <c r="R105" t="n">
-        <v>7040848</v>
+        <v>7040831</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11783,7 +11783,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119862752</v>
+        <v>119862769</v>
       </c>
       <c r="B106" t="n">
         <v>90864</v>
@@ -11823,10 +11823,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>585403</v>
+        <v>585361</v>
       </c>
       <c r="R106" t="n">
-        <v>7040860</v>
+        <v>7040752</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11885,10 +11885,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119862758</v>
+        <v>119862753</v>
       </c>
       <c r="B107" t="n">
-        <v>57320</v>
+        <v>95478</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11901,54 +11901,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>585399</v>
+        <v>585405</v>
       </c>
       <c r="R107" t="n">
-        <v>7040847</v>
+        <v>7040862</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11981,11 +11961,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12012,10 +11987,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119862769</v>
+        <v>119862758</v>
       </c>
       <c r="B108" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12028,34 +12003,54 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>585361</v>
+        <v>585399</v>
       </c>
       <c r="R108" t="n">
-        <v>7040752</v>
+        <v>7040847</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12088,6 +12083,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Noterad i gammal granskog, bara ca femtio meter ifrån en ung tretåig. Eventuell förälder?</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12114,10 +12114,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119862763</v>
+        <v>119862762</v>
       </c>
       <c r="B109" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12130,21 +12130,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12154,10 +12154,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>585388</v>
+        <v>585380</v>
       </c>
       <c r="R109" t="n">
-        <v>7040836</v>
+        <v>7040800</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12216,10 +12216,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119862753</v>
+        <v>119862768</v>
       </c>
       <c r="B110" t="n">
-        <v>95478</v>
+        <v>90594</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12232,21 +12232,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12256,10 +12256,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>585405</v>
+        <v>585352</v>
       </c>
       <c r="R110" t="n">
-        <v>7040862</v>
+        <v>7040764</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12318,10 +12318,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119862768</v>
+        <v>119862767</v>
       </c>
       <c r="B111" t="n">
-        <v>90594</v>
+        <v>90545</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12330,25 +12330,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12358,10 +12358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>585352</v>
+        <v>585354</v>
       </c>
       <c r="R111" t="n">
-        <v>7040764</v>
+        <v>7040772</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12420,10 +12420,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119862810</v>
+        <v>119862764</v>
       </c>
       <c r="B112" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12436,42 +12436,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>585359</v>
+        <v>585387</v>
       </c>
       <c r="R112" t="n">
-        <v>7041095</v>
+        <v>7040839</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12530,10 +12522,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119862767</v>
+        <v>119862754</v>
       </c>
       <c r="B113" t="n">
-        <v>90545</v>
+        <v>90594</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12542,25 +12534,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12570,10 +12562,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>585354</v>
+        <v>585410</v>
       </c>
       <c r="R113" t="n">
-        <v>7040772</v>
+        <v>7040863</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12632,10 +12624,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119862760</v>
+        <v>119862752</v>
       </c>
       <c r="B114" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12644,25 +12636,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12672,10 +12664,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>585372</v>
+        <v>585403</v>
       </c>
       <c r="R114" t="n">
-        <v>7040881</v>
+        <v>7040860</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12734,10 +12726,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119862764</v>
+        <v>119862810</v>
       </c>
       <c r="B115" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12750,34 +12742,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fjällsjöälven N Kilåmon, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>585387</v>
+        <v>585359</v>
       </c>
       <c r="R115" t="n">
-        <v>7040839</v>
+        <v>7041095</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12834,6 +12834,521 @@
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>123231136</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>585384</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7041145</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>123236444</v>
+      </c>
+      <c r="B117" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>585270</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7041198</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>123236145</v>
+      </c>
+      <c r="B118" t="n">
+        <v>90917</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>585269</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7041239</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>123236869</v>
+      </c>
+      <c r="B119" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>585327</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7041140</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>123236897</v>
+      </c>
+      <c r="B120" t="n">
+        <v>90948</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>585327</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7041140</v>
+      </c>
+      <c r="S120" t="n">
+        <v>15</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12836,10 +12836,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B116" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12852,39 +12852,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R116" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12943,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123236444</v>
+        <v>123231136</v>
       </c>
       <c r="B117" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12959,34 +12954,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585270</v>
+        <v>585384</v>
       </c>
       <c r="R117" t="n">
-        <v>7041198</v>
+        <v>7041145</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12836,10 +12836,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123236444</v>
+        <v>123236869</v>
       </c>
       <c r="B116" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12852,21 +12852,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12876,10 +12876,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>585270</v>
+        <v>585327</v>
       </c>
       <c r="R116" t="n">
-        <v>7041198</v>
+        <v>7041140</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123231136</v>
+        <v>123236145</v>
       </c>
       <c r="B117" t="n">
-        <v>57494</v>
+        <v>90917</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12950,43 +12950,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585384</v>
+        <v>585269</v>
       </c>
       <c r="R117" t="n">
-        <v>7041145</v>
+        <v>7041239</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13045,10 +13040,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123236145</v>
+        <v>123236444</v>
       </c>
       <c r="B118" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13057,25 +13052,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13085,10 +13080,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>585269</v>
+        <v>585270</v>
       </c>
       <c r="R118" t="n">
-        <v>7041239</v>
+        <v>7041198</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13147,10 +13142,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123236869</v>
+        <v>123231136</v>
       </c>
       <c r="B119" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13163,34 +13158,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585327</v>
+        <v>585384</v>
       </c>
       <c r="R119" t="n">
-        <v>7041140</v>
+        <v>7041145</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12836,10 +12836,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123236869</v>
+        <v>123236897</v>
       </c>
       <c r="B116" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12852,21 +12852,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123236145</v>
+        <v>123236869</v>
       </c>
       <c r="B117" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12950,25 +12950,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585269</v>
+        <v>585327</v>
       </c>
       <c r="R117" t="n">
-        <v>7041239</v>
+        <v>7041140</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13040,10 +13040,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123236444</v>
+        <v>123231136</v>
       </c>
       <c r="B118" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13056,34 +13056,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>585270</v>
+        <v>585384</v>
       </c>
       <c r="R118" t="n">
-        <v>7041198</v>
+        <v>7041145</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13142,10 +13147,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B119" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13158,39 +13163,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R119" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13249,10 +13249,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123236897</v>
+        <v>123236145</v>
       </c>
       <c r="B120" t="n">
-        <v>90948</v>
+        <v>90917</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13261,25 +13261,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13289,10 +13289,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>585327</v>
+        <v>585269</v>
       </c>
       <c r="R120" t="n">
-        <v>7041140</v>
+        <v>7041239</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12836,10 +12836,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123236897</v>
+        <v>123236869</v>
       </c>
       <c r="B116" t="n">
-        <v>90948</v>
+        <v>78769</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12852,21 +12852,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123236869</v>
+        <v>123236444</v>
       </c>
       <c r="B117" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12954,21 +12954,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585327</v>
+        <v>585270</v>
       </c>
       <c r="R117" t="n">
-        <v>7041140</v>
+        <v>7041198</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13040,10 +13040,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123231136</v>
+        <v>123236897</v>
       </c>
       <c r="B118" t="n">
-        <v>57494</v>
+        <v>90951</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13056,39 +13056,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>585384</v>
+        <v>585327</v>
       </c>
       <c r="R118" t="n">
-        <v>7041145</v>
+        <v>7041140</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13147,10 +13142,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123236444</v>
+        <v>123236145</v>
       </c>
       <c r="B119" t="n">
-        <v>90952</v>
+        <v>90920</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13159,25 +13154,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13187,10 +13182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585270</v>
+        <v>585269</v>
       </c>
       <c r="R119" t="n">
-        <v>7041198</v>
+        <v>7041239</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13249,10 +13244,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123236145</v>
+        <v>123231136</v>
       </c>
       <c r="B120" t="n">
-        <v>90917</v>
+        <v>57497</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13261,38 +13256,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>585269</v>
+        <v>585384</v>
       </c>
       <c r="R120" t="n">
-        <v>7041239</v>
+        <v>7041145</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12836,10 +12836,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123236869</v>
+        <v>123236145</v>
       </c>
       <c r="B116" t="n">
-        <v>78769</v>
+        <v>90922</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12848,25 +12848,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12876,10 +12876,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>585327</v>
+        <v>585269</v>
       </c>
       <c r="R116" t="n">
-        <v>7041140</v>
+        <v>7041239</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123236444</v>
+        <v>123231136</v>
       </c>
       <c r="B117" t="n">
-        <v>90955</v>
+        <v>57497</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12954,34 +12954,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585270</v>
+        <v>585384</v>
       </c>
       <c r="R117" t="n">
-        <v>7041198</v>
+        <v>7041145</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13043,7 +13048,7 @@
         <v>123236897</v>
       </c>
       <c r="B118" t="n">
-        <v>90951</v>
+        <v>90953</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13142,10 +13147,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123236145</v>
+        <v>123236869</v>
       </c>
       <c r="B119" t="n">
-        <v>90920</v>
+        <v>78771</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13154,25 +13159,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13182,10 +13187,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585269</v>
+        <v>585327</v>
       </c>
       <c r="R119" t="n">
-        <v>7041239</v>
+        <v>7041140</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13244,10 +13249,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B120" t="n">
-        <v>57497</v>
+        <v>90957</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13260,39 +13265,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R120" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12836,10 +12836,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123236145</v>
+        <v>123236869</v>
       </c>
       <c r="B116" t="n">
-        <v>90922</v>
+        <v>78772</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12848,25 +12848,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12876,10 +12876,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>585269</v>
+        <v>585327</v>
       </c>
       <c r="R116" t="n">
-        <v>7041239</v>
+        <v>7041140</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B117" t="n">
-        <v>57497</v>
+        <v>90963</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12954,39 +12954,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R117" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13048,7 +13043,7 @@
         <v>123236897</v>
       </c>
       <c r="B118" t="n">
-        <v>90953</v>
+        <v>90959</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13147,10 +13142,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123236869</v>
+        <v>123236145</v>
       </c>
       <c r="B119" t="n">
-        <v>78771</v>
+        <v>90928</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13159,25 +13154,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13187,10 +13182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585327</v>
+        <v>585269</v>
       </c>
       <c r="R119" t="n">
-        <v>7041140</v>
+        <v>7041239</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13249,10 +13244,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123236444</v>
+        <v>123231136</v>
       </c>
       <c r="B120" t="n">
-        <v>90957</v>
+        <v>57497</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13265,34 +13260,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>585270</v>
+        <v>585384</v>
       </c>
       <c r="R120" t="n">
-        <v>7041198</v>
+        <v>7041145</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12839,7 +12839,7 @@
         <v>123236897</v>
       </c>
       <c r="B116" t="n">
-        <v>90962</v>
+        <v>90979</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123231136</v>
+        <v>123236444</v>
       </c>
       <c r="B117" t="n">
-        <v>57497</v>
+        <v>90983</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12954,39 +12954,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585384</v>
+        <v>585270</v>
       </c>
       <c r="R117" t="n">
-        <v>7041145</v>
+        <v>7041198</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13048,7 +13043,7 @@
         <v>123236869</v>
       </c>
       <c r="B118" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13147,10 +13142,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123236145</v>
+        <v>123231136</v>
       </c>
       <c r="B119" t="n">
-        <v>90931</v>
+        <v>57503</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13159,38 +13154,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585269</v>
+        <v>585384</v>
       </c>
       <c r="R119" t="n">
-        <v>7041239</v>
+        <v>7041145</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13249,10 +13249,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123236444</v>
+        <v>123236145</v>
       </c>
       <c r="B120" t="n">
-        <v>90966</v>
+        <v>90948</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13261,25 +13261,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13289,10 +13289,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>585270</v>
+        <v>585269</v>
       </c>
       <c r="R120" t="n">
-        <v>7041198</v>
+        <v>7041239</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12839,7 +12839,7 @@
         <v>123236897</v>
       </c>
       <c r="B116" t="n">
-        <v>90979</v>
+        <v>90984</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>123236444</v>
       </c>
       <c r="B117" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>123236869</v>
       </c>
       <c r="B118" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>123231136</v>
       </c>
       <c r="B119" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>123236145</v>
       </c>
       <c r="B120" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12839,7 +12839,7 @@
         <v>123236897</v>
       </c>
       <c r="B116" t="n">
-        <v>90984</v>
+        <v>90986</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123236444</v>
+        <v>123236145</v>
       </c>
       <c r="B117" t="n">
-        <v>90988</v>
+        <v>90955</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12950,25 +12950,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585270</v>
+        <v>585269</v>
       </c>
       <c r="R117" t="n">
-        <v>7041198</v>
+        <v>7041239</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13043,7 +13043,7 @@
         <v>123236869</v>
       </c>
       <c r="B118" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>123231136</v>
       </c>
       <c r="B119" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13249,10 +13249,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123236145</v>
+        <v>123236444</v>
       </c>
       <c r="B120" t="n">
-        <v>90953</v>
+        <v>90990</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13261,25 +13261,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13289,10 +13289,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>585269</v>
+        <v>585270</v>
       </c>
       <c r="R120" t="n">
-        <v>7041239</v>
+        <v>7041198</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>

--- a/artfynd/A 20509-2024 artfynd.xlsx
+++ b/artfynd/A 20509-2024 artfynd.xlsx
@@ -12836,10 +12836,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123236897</v>
+        <v>123236869</v>
       </c>
       <c r="B116" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12852,21 +12852,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12938,10 +12938,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123236145</v>
+        <v>123236897</v>
       </c>
       <c r="B117" t="n">
-        <v>90955</v>
+        <v>90986</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12950,25 +12950,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>585269</v>
+        <v>585327</v>
       </c>
       <c r="R117" t="n">
-        <v>7041239</v>
+        <v>7041140</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13040,10 +13040,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123236869</v>
+        <v>123231136</v>
       </c>
       <c r="B118" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13056,34 +13056,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>585327</v>
+        <v>585384</v>
       </c>
       <c r="R118" t="n">
-        <v>7041140</v>
+        <v>7041145</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13142,10 +13147,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123231136</v>
+        <v>123236145</v>
       </c>
       <c r="B119" t="n">
-        <v>57507</v>
+        <v>90955</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13154,43 +13159,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>585384</v>
+        <v>585269</v>
       </c>
       <c r="R119" t="n">
-        <v>7041145</v>
+        <v>7041239</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
